--- a/ihris5/publisher/ValueSet-ihris-document-category.xlsx
+++ b/ihris5/publisher/ValueSet-ihris-document-category.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-09T12:24:20+00:00</t>
+    <t>2026-10-09T12:31:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ihris5/publisher/ValueSet-ihris-document-category.xlsx
+++ b/ihris5/publisher/ValueSet-ihris-document-category.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-09T12:31:23+00:00</t>
+    <t>2026-10-10T05:51:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ihris5/publisher/ValueSet-ihris-document-category.xlsx
+++ b/ihris5/publisher/ValueSet-ihris-document-category.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-10T05:51:05+00:00</t>
+    <t>2026-10-11T05:58:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
